--- a/Result/profitability/3691.xlsx
+++ b/Result/profitability/3691.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM72"/>
+  <dimension ref="A1:AM73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>-1.62</v>
       </c>
       <c r="M2" t="n">
-        <v>-1.52625</v>
+        <v>-1.2475</v>
       </c>
       <c r="N2" t="n">
-        <v>5.5875</v>
+        <v>6.296250000000001</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>3.63</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.8412500000000002</v>
+        <v>-0.2825000000000002</v>
       </c>
       <c r="N3" t="n">
-        <v>10.37375</v>
+        <v>12.32125</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -899,10 +899,10 @@
         <v>3.37</v>
       </c>
       <c r="M4" t="n">
-        <v>0.09124999999999983</v>
+        <v>0.2637499999999998</v>
       </c>
       <c r="N4" t="n">
-        <v>17.24375</v>
+        <v>17.9</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -1018,10 +1018,10 @@
         <v>4.35</v>
       </c>
       <c r="M5" t="n">
-        <v>0.7599999999999998</v>
+        <v>1.55875</v>
       </c>
       <c r="N5" t="n">
-        <v>22.95</v>
+        <v>23.73125</v>
       </c>
       <c r="O5" t="n">
         <v>1</v>
@@ -1137,10 +1137,10 @@
         <v>3.77</v>
       </c>
       <c r="M6" t="n">
-        <v>1.9825</v>
+        <v>2.1725</v>
       </c>
       <c r="N6" t="n">
-        <v>28.60625</v>
+        <v>28.50125</v>
       </c>
       <c r="O6" t="n">
         <v>1</v>
@@ -1264,10 +1264,10 @@
         <v>7.53</v>
       </c>
       <c r="M7" t="n">
-        <v>3.06625</v>
+        <v>3.047499999999999</v>
       </c>
       <c r="N7" t="n">
-        <v>33.35875</v>
+        <v>33.37125</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -1391,10 +1391,10 @@
         <v>8.01</v>
       </c>
       <c r="M8" t="n">
-        <v>4.00125</v>
+        <v>3.6775</v>
       </c>
       <c r="N8" t="n">
-        <v>38.6425</v>
+        <v>37.68375</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -1772,7 +1772,7 @@
         <v>10.93</v>
       </c>
       <c r="M11" t="n">
-        <v>7.078749999999999</v>
+        <v>7.07875</v>
       </c>
       <c r="N11" t="n">
         <v>52.52375</v>
@@ -9572,6 +9572,133 @@
       </c>
       <c r="AM72" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>3691</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C73" t="n">
+        <v>2643</v>
+      </c>
+      <c r="D73" t="n">
+        <v>2363</v>
+      </c>
+      <c r="E73" t="n">
+        <v>280</v>
+      </c>
+      <c r="F73" t="n">
+        <v>10.61</v>
+      </c>
+      <c r="G73" t="n">
+        <v>1</v>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>0.03%</t>
+        </is>
+      </c>
+      <c r="I73" t="n">
+        <v>85</v>
+      </c>
+      <c r="J73" t="n">
+        <v>86</v>
+      </c>
+      <c r="K73" t="n">
+        <v>34</v>
+      </c>
+      <c r="L73" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="M73" t="n">
+        <v>-1.27625</v>
+      </c>
+      <c r="N73" t="n">
+        <v>7.5675</v>
+      </c>
+      <c r="O73" t="n">
+        <v>1</v>
+      </c>
+      <c r="P73" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q73" t="n">
+        <v>0</v>
+      </c>
+      <c r="R73" t="n">
+        <v>0</v>
+      </c>
+      <c r="S73" t="n">
+        <v>1</v>
+      </c>
+      <c r="T73" t="n">
+        <v>0</v>
+      </c>
+      <c r="U73" t="n">
+        <v>0</v>
+      </c>
+      <c r="V73" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W73" t="n">
+        <v>-2.59</v>
+      </c>
+      <c r="X73" t="n">
+        <v>-0.8720538720538721</v>
+      </c>
+      <c r="Y73" t="n">
+        <v>-7.670000000000002</v>
+      </c>
+      <c r="Z73" t="n">
+        <v>-0.4195842450765865</v>
+      </c>
+      <c r="AA73" t="n">
+        <v>6.39</v>
+      </c>
+      <c r="AB73" t="n">
+        <v>-1.063227953410982</v>
+      </c>
+      <c r="AC73" t="n">
+        <v>6.249999999999999</v>
+      </c>
+      <c r="AD73" t="n">
+        <v>1.43348623853211</v>
+      </c>
+      <c r="AE73" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF73" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG73" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH73" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI73" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ73" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK73" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL73" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM73" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
